--- a/hyp_rep_27022026.xlsx
+++ b/hyp_rep_27022026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demanet\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3B94A7-1C2D-4FDE-A2A3-181112414C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0924BF7E-8F9D-48CE-B7A3-9D1B7995A258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="-13785" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34230" yWindow="-11625" windowWidth="21600" windowHeight="11295" firstSheet="25" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C2F_ABCDT1" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,10 @@
     <sheet name="salle_M_Salle_M" sheetId="28" r:id="rId28"/>
     <sheet name="salle_M_salle_K" sheetId="29" r:id="rId29"/>
     <sheet name="salle_M_salle_L" sheetId="30" r:id="rId30"/>
+    <sheet name="C2A_C2A" sheetId="31" r:id="rId31"/>
+    <sheet name="C2A_C2C" sheetId="32" r:id="rId32"/>
+    <sheet name="C2C_C2A" sheetId="33" r:id="rId33"/>
+    <sheet name="C2C_C2C" sheetId="34" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="19">
   <si>
     <t>heure</t>
   </si>
@@ -125,8 +129,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -142,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -150,12 +162,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7992,6 +8022,1326 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0412F58C-2AF8-45C9-8E9F-07B1B033336F}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.5</v>
+      </c>
+      <c r="H6">
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>0.5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747D1BE3-A50B-4F11-BEEA-80B702CA221A}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.5</v>
+      </c>
+      <c r="H6">
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>0.5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15804357-406A-4013-AD07-D2EFD90FA48D}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.5</v>
+      </c>
+      <c r="H6">
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>0.5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60B13FF-6F7C-4BEC-97BD-843A1AEA40EC}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.5</v>
+      </c>
+      <c r="H6">
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <v>0.5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>0.5</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <v>0.5</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L8"/>
